--- a/Title 24 Mandatory Requirements.xlsx
+++ b/Title 24 Mandatory Requirements.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git Projects\PsychroCalc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9F580CC-D0A3-4EAD-A06E-1F879136ADDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD641C62-8D0E-4CEF-9EB4-540EE22486AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1404" yWindow="1272" windowWidth="21492" windowHeight="12000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -362,7 +362,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C3:E3"/>
+  <dimension ref="C3:N17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="11.44140625" bestFit="1" customWidth="1"/>
@@ -370,7 +370,7 @@
     <col min="5" max="5" width="5.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C3" t="s">
         <v>0</v>
       </c>
@@ -379,6 +379,16 @@
       </c>
       <c r="E3" t="s">
         <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="N16">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="17" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N17">
+        <v>13700</v>
       </c>
     </row>
   </sheetData>
